--- a/data/lossofsale_sg_palakkad.xlsx
+++ b/data/lossofsale_sg_palakkad.xlsx
@@ -2868,6 +2868,644 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="65">
+        <v>50</v>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">surendhranath</t>
+        </is>
+      </c>
+      <c r="D52" s="65">
+        <v>9895637821</v>
+      </c>
+      <c t="inlineStr" r="E52">
+        <is>
+          <t xml:space="preserve">18-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F52">
+        <is>
+          <t xml:space="preserve">NAVAS A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G52">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H52">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I52">
+        <is>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J52">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K52">
+        <is>
+          <t xml:space="preserve">groom not comming</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65">
+        <v>51</v>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">DHILEEP</t>
+        </is>
+      </c>
+      <c r="D53" s="65">
+        <v>7012940657</v>
+      </c>
+      <c t="inlineStr" r="E53">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F53">
+        <is>
+          <t xml:space="preserve">MUHAMMED YASHEER M A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G53">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H53">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I53">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J53">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K53">
+        <is>
+          <t xml:space="preserve">customernu product ishttapettilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="65">
+        <v>52</v>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">jaseel</t>
+        </is>
+      </c>
+      <c r="D54" s="65">
+        <v>6282925074</v>
+      </c>
+      <c t="inlineStr" r="E54">
+        <is>
+          <t xml:space="preserve">31-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F54">
+        <is>
+          <t xml:space="preserve">ASHIK A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G54">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H54">
+        <is>
+          <t xml:space="preserve">PRICING</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I54">
+        <is>
+          <t xml:space="preserve">RENT TO HIGH</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J54">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K54">
+        <is>
+          <t xml:space="preserve">price kuduthal ..nokittu parayam</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="65">
+        <v>53</v>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">vaishakh</t>
+        </is>
+      </c>
+      <c r="D55" s="65">
+        <v>8075100440</v>
+      </c>
+      <c t="inlineStr" r="E55">
+        <is>
+          <t xml:space="preserve">25-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F55">
+        <is>
+          <t xml:space="preserve">ASHIK A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G55">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H55">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I55">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J55">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K55">
+        <is>
+          <t xml:space="preserve">next Sunday varam</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="65">
+        <v>54</v>
+      </c>
+      <c t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">pristo</t>
+        </is>
+      </c>
+      <c r="D56" s="65">
+        <v>8606878997</v>
+      </c>
+      <c t="inlineStr" r="E56">
+        <is>
+          <t xml:space="preserve">10-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F56">
+        <is>
+          <t xml:space="preserve">NAVAS A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G56">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H56">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I56">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J56">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K56">
+        <is>
+          <t xml:space="preserve">comming next week</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="65">
+        <v>55</v>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">alfin</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D57">
+        <is>
+          <t xml:space="preserve">0547952954</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E57">
+        <is>
+          <t xml:space="preserve">18-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F57">
+        <is>
+          <t xml:space="preserve">NAVAS A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G57">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H57">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I57">
+        <is>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J57">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K57">
+        <is>
+          <t xml:space="preserve">bangala 44 size not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="65">
+        <v>56</v>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">fayas</t>
+        </is>
+      </c>
+      <c r="D58" s="65">
+        <v>6282843704</v>
+      </c>
+      <c t="inlineStr" r="E58">
+        <is>
+          <t xml:space="preserve">11-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F58">
+        <is>
+          <t xml:space="preserve">ASHIK A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G58">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H58">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I58">
+        <is>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J58">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K58">
+        <is>
+          <t xml:space="preserve">nalek vara</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65">
+        <v>57</v>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">SUJITH</t>
+        </is>
+      </c>
+      <c r="D59" s="65">
+        <v>9633930742</v>
+      </c>
+      <c t="inlineStr" r="E59">
+        <is>
+          <t xml:space="preserve">17-05-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F59">
+        <is>
+          <t xml:space="preserve">MUHAMMED YASHEER M A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G59">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H59">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I59">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J59">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K59">
+        <is>
+          <t xml:space="preserve">long date ann pinneed vannu nokkam enn parannu</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="65">
+        <v>58</v>
+      </c>
+      <c t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C60">
+        <is>
+          <t xml:space="preserve">bava shihad</t>
+        </is>
+      </c>
+      <c r="D60" s="65">
+        <v>9847963660</v>
+      </c>
+      <c t="inlineStr" r="E60">
+        <is>
+          <t xml:space="preserve">12-04-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F60">
+        <is>
+          <t xml:space="preserve">ASHIK A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G60">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H60">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I60">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J60">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K60">
+        <is>
+          <t xml:space="preserve">groom abroad ahha vannittilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="65">
+        <v>59</v>
+      </c>
+      <c t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C61">
+        <is>
+          <t xml:space="preserve">visnhu raj</t>
+        </is>
+      </c>
+      <c r="D61" s="65">
+        <v>9496952056</v>
+      </c>
+      <c t="inlineStr" r="E61">
+        <is>
+          <t xml:space="preserve">01-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F61">
+        <is>
+          <t xml:space="preserve">ASHIK A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G61">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H61">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I61">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J61">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K61">
+        <is>
+          <t xml:space="preserve">bride nte costume eduthitt illa eduthitt varum</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="65">
+        <v>60</v>
+      </c>
+      <c t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C62">
+        <is>
+          <t xml:space="preserve">VINEETH</t>
+        </is>
+      </c>
+      <c r="D62" s="65">
+        <v>9562131056</v>
+      </c>
+      <c t="inlineStr" r="E62">
+        <is>
+          <t xml:space="preserve">09-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F62">
+        <is>
+          <t xml:space="preserve">MUHAMMED YASHEER M A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G62">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H62">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I62">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J62">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K62">
+        <is>
+          <t xml:space="preserve">nokeet vara parannu</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="65">
+        <v>61</v>
+      </c>
+      <c t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C63">
+        <is>
+          <t xml:space="preserve">ARSHAD</t>
+        </is>
+      </c>
+      <c r="D63" s="65">
+        <v>7593933877</v>
+      </c>
+      <c t="inlineStr" r="E63">
+        <is>
+          <t xml:space="preserve">08-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F63">
+        <is>
+          <t xml:space="preserve">MUHAMMED YASHEER M A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G63">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H63">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I63">
+        <is>
+          <t xml:space="preserve">BUDGET RESTRICTIONS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J63">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K63">
+        <is>
+          <t xml:space="preserve">rate kooduthal ayath kond eduthilla</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
